--- a/project-management/Project_Schedule_Gantt_Template.xlsx
+++ b/project-management/Project_Schedule_Gantt_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFCDABC-5EB3-4064-BB39-F3FD1AFFE979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C784AAE-FEDB-4AA8-AC21-D8A5246F44B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,7 +266,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,8 +288,33 @@
         <fgColor rgb="FF2778C9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -301,8 +326,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -327,11 +353,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFCFE5F7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -339,15 +375,14 @@
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFCFE5F7"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFA6C9EC"/>
+      <color rgb="FFFFFFFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -366,9 +401,9 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Actividad"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Responsable"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Inicio"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Fin" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Fin" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Duración (días)"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Dependencia" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Dependencia" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Hito"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Estado"/>
   </tableColumns>
@@ -585,661 +620,811 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
     </row>
     <row r="2" spans="1:22" ht="22.35" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
     </row>
     <row r="4" spans="1:22" ht="22.35" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="3">
         <v>46265</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="3">
         <v>46272</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="3">
         <v>46279</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="3">
         <v>46286</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4" s="3">
         <v>46293</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="3">
         <v>46300</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="3">
         <v>46307</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="3">
         <v>46314</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="3">
         <v>46321</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" s="3">
         <v>46328</v>
       </c>
-      <c r="U4" s="2">
+      <c r="U4" s="3">
         <v>46335</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" s="3">
         <v>46342</v>
       </c>
     </row>
     <row r="5" spans="1:22">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>46265</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>46346</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <f t="shared" ref="F5:F28" si="0">E5-D5+1</f>
         <v>82</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="12">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="12">
         <v>1</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="12">
         <v>1</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="12">
         <v>1</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="12">
         <v>1</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="12">
         <v>1</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="12">
         <v>1</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="12">
         <v>1</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="12">
         <v>1</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="12">
         <v>1</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="12">
         <v>1</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>46265</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>46269</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>1.1000000000000001</v>
       </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>46265</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>46267</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>46268</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>46269</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>46272</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>46290</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="L9">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1">
         <v>1.2</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>1.2</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>1.2</v>
       </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>46272</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>46274</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="L10" t="s">
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>46273</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>46275</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="L11" t="s">
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>46274</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>46276</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="L12" t="s">
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>46276</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>46276</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="L13" t="s">
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C14" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>46279</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>46280</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M14" t="s">
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C15" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>46280</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>46281</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M15" t="s">
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
     </row>
     <row r="16" spans="1:22" ht="27.6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C16" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>46281</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>46283</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M16" t="s">
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
     </row>
     <row r="17" spans="1:22">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <v>46283</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <v>46287</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M17" t="s">
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N17" s="11" t="s">
         <v>25</v>
       </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <v>46286</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>46288</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="N18" t="s">
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="11" t="s">
         <v>26</v>
       </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C19" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <v>46287</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>46290</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="N19" t="s">
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
@@ -1251,17 +1436,17 @@
       <c r="C20" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>46293</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>46295</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="9">
         <v>1.2</v>
       </c>
       <c r="H20" t="s">
@@ -1270,21 +1455,28 @@
       <c r="I20" t="s">
         <v>68</v>
       </c>
-      <c r="O20">
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="10">
         <v>1.3</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="10">
         <v>1.3</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="10">
         <v>1.3</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="10">
         <v>1.3</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="10">
         <v>1.3</v>
       </c>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
@@ -1296,17 +1488,17 @@
       <c r="C21" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>46293</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>46297</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="9" t="s">
         <v>18</v>
       </c>
       <c r="H21" t="s">
@@ -1315,9 +1507,20 @@
       <c r="I21" t="s">
         <v>68</v>
       </c>
-      <c r="O21" t="s">
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="10" t="s">
         <v>29</v>
       </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
@@ -1329,31 +1532,41 @@
       <c r="C22" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>46300</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>46307</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="9" t="s">
         <v>19</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P22" t="s">
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="Q22" s="10" t="s">
         <v>30</v>
       </c>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
@@ -1365,31 +1578,41 @@
       <c r="C23" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>46307</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>46314</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="9" t="s">
         <v>20</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="R23" t="s">
+      <c r="R23" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
@@ -1401,31 +1624,41 @@
       <c r="C24" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <v>46314</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>46325</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="9" t="s">
         <v>27</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="R24" t="s">
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="S24" t="s">
+      <c r="S24" s="10" t="s">
         <v>32</v>
       </c>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
@@ -1437,31 +1670,41 @@
       <c r="C25" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <v>46328</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <v>46339</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="9">
         <v>1.3</v>
       </c>
       <c r="H25" t="s">
         <v>67</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="T25">
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="10">
         <v>1.4</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="10">
         <v>1.4</v>
       </c>
+      <c r="V25" s="1"/>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
@@ -1473,28 +1716,39 @@
       <c r="C26" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>46328</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <v>46332</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="T26" t="s">
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="10" t="s">
         <v>34</v>
       </c>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
@@ -1506,28 +1760,39 @@
       <c r="C27" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>46335</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <v>46339</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="9" t="s">
         <v>34</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="U27" t="s">
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="10" t="s">
         <v>35</v>
       </c>
+      <c r="V27" s="1"/>
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
@@ -1539,26 +1804,37 @@
       <c r="C28" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>46342</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <v>46346</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="9" t="s">
         <v>35</v>
       </c>
       <c r="H28" t="s">
         <v>67</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="V28">
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="10">
         <v>1.5</v>
       </c>
     </row>
@@ -1568,7 +1844,7 @@
     <mergeCell ref="A2:V2"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:V19">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(K$4&lt;=$E5,K$4+6&gt;=$D5)</formula>
     </cfRule>
   </conditionalFormatting>
